--- a/research/traditional_assets/database/data/turkey/turkey_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.716</v>
+        <v>0.341</v>
       </c>
       <c r="E2">
-        <v>1.085</v>
+        <v>0.92</v>
       </c>
       <c r="G2">
-        <v>1.94015410594316e-05</v>
+        <v>1.073653868550798e-05</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -606,91 +606,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>232.204</v>
+        <v>223.708</v>
       </c>
       <c r="L2">
-        <v>0.01155157805170322</v>
+        <v>0.01356977173026903</v>
       </c>
       <c r="M2">
-        <v>43.38</v>
+        <v>37.82</v>
       </c>
       <c r="N2">
-        <v>0.03638712274992031</v>
+        <v>0.01491248477010248</v>
       </c>
       <c r="O2">
-        <v>0.1868184871922964</v>
+        <v>0.1690596670659968</v>
       </c>
       <c r="P2">
-        <v>43.38</v>
+        <v>33.28</v>
       </c>
       <c r="Q2">
-        <v>0.03638712274992031</v>
+        <v>0.01312235571520387</v>
       </c>
       <c r="R2">
-        <v>0.1868184871922964</v>
+        <v>0.1487653548375561</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1200423056583818</v>
       </c>
       <c r="U2">
-        <v>158.946</v>
+        <v>130.958</v>
       </c>
       <c r="V2">
-        <v>0.1333238269388851</v>
+        <v>0.05163694290119197</v>
       </c>
       <c r="W2">
-        <v>0.6692021636240704</v>
+        <v>0.4552727272727273</v>
       </c>
       <c r="X2">
-        <v>0.06588015369437752</v>
+        <v>0.1350587122855602</v>
       </c>
       <c r="Y2">
-        <v>0.6033220099296929</v>
+        <v>0.3202140149871671</v>
       </c>
       <c r="Z2">
-        <v>41.8988915337188</v>
+        <v>26.24790830452857</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06481578184551499</v>
+        <v>0.1284682141320884</v>
       </c>
       <c r="AC2">
-        <v>-0.06481578184551499</v>
+        <v>-0.1284682141320884</v>
       </c>
       <c r="AD2">
-        <v>269.708</v>
+        <v>718.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>269.708</v>
+        <v>718.2</v>
       </c>
       <c r="AG2">
-        <v>110.762</v>
+        <v>587.2420000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1844929296909202</v>
+        <v>0.2206905876171132</v>
       </c>
       <c r="AI2">
-        <v>0.3330764632947534</v>
+        <v>0.5940741476003772</v>
       </c>
       <c r="AJ2">
-        <v>0.0850091562018877</v>
+        <v>0.1880153884967913</v>
       </c>
       <c r="AK2">
-        <v>0.1701930848399359</v>
+        <v>0.5447604876519275</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-23.15</v>
+        <v>-34.856</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Inveo Yatirim Holding A.S. (IBSE:INVEO)</t>
+          <t>Inveo Yatirim Holding Anonim Sirketi (IBSE:INVEO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.736</v>
+        <v>0.339</v>
       </c>
       <c r="E3">
-        <v>1.299</v>
+        <v>2.279</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,19 +731,19 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>41.5</v>
+        <v>58.6</v>
       </c>
       <c r="L3">
-        <v>1.985645933014354</v>
+        <v>16.46067415730337</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>2.38</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.006001008572869389</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.04061433447098976</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,64 +755,70 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>2.38</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.028</v>
+        <v>0.002</v>
       </c>
       <c r="V3">
-        <v>0.000445859872611465</v>
+        <v>5.042864346949067e-06</v>
       </c>
       <c r="W3">
-        <v>0.7319223985890653</v>
+        <v>0.6460859977949284</v>
       </c>
       <c r="X3">
-        <v>0.05802573090641412</v>
+        <v>0.1212995854340401</v>
       </c>
       <c r="Y3">
-        <v>0.6738966676826511</v>
+        <v>0.5247864123608883</v>
       </c>
       <c r="Z3">
-        <v>0.3439763001974983</v>
+        <v>0.03922432789775232</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05803795355882341</v>
+        <v>0.1203113334454893</v>
       </c>
       <c r="AC3">
-        <v>-0.05803795355882341</v>
+        <v>-0.1203113334454893</v>
       </c>
       <c r="AD3">
-        <v>0.08799999999999999</v>
+        <v>28.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.08799999999999999</v>
+        <v>28.4</v>
       </c>
       <c r="AG3">
-        <v>0.06</v>
+        <v>28.398</v>
       </c>
       <c r="AH3">
-        <v>0.001399313064495611</v>
+        <v>0.0668235294117647</v>
       </c>
       <c r="AI3">
-        <v>0.000969291095739525</v>
+        <v>0.2019914651493599</v>
       </c>
       <c r="AJ3">
-        <v>0.0009545020680878141</v>
+        <v>0.06681913797241398</v>
       </c>
       <c r="AK3">
-        <v>0.0006610841780520053</v>
+        <v>0.2019801135151282</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-2.21</v>
+      </c>
+      <c r="AQ3">
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Is Yatirim Menkul Degerler Anonim Sirketi (IBSE:ISMEN)</t>
+          <t>Oyak Yatirim Menkul Degerler A.S. (IBSE:OYYAT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.177</v>
+        <v>0.312</v>
       </c>
       <c r="E4">
-        <v>0.871</v>
+        <v>1.148</v>
       </c>
       <c r="G4">
-        <v>3.023349561226705e-05</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -850,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>137.5</v>
+        <v>33.9</v>
       </c>
       <c r="L4">
-        <v>0.01065924524791466</v>
+        <v>0.02609498883842661</v>
       </c>
       <c r="M4">
-        <v>40</v>
+        <v>5.4</v>
       </c>
       <c r="N4">
-        <v>0.06373486297004462</v>
+        <v>0.008749189889825017</v>
       </c>
       <c r="O4">
-        <v>0.2909090909090909</v>
+        <v>0.1592920353982301</v>
       </c>
       <c r="P4">
-        <v>40</v>
+        <v>5.4</v>
       </c>
       <c r="Q4">
-        <v>0.06373486297004462</v>
+        <v>0.008749189889825017</v>
       </c>
       <c r="R4">
-        <v>0.2909090909090909</v>
+        <v>0.1592920353982301</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,61 +886,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>79.3</v>
+        <v>42</v>
       </c>
       <c r="V4">
-        <v>0.1263543658381134</v>
+        <v>0.06804925469863901</v>
       </c>
       <c r="W4">
-        <v>0.6773399014778325</v>
+        <v>0.4863701578192252</v>
       </c>
       <c r="X4">
-        <v>0.06160682535306186</v>
+        <v>0.1251724449064209</v>
       </c>
       <c r="Y4">
-        <v>0.6157330761247707</v>
+        <v>0.3611977129128043</v>
       </c>
       <c r="Z4">
-        <v>49.08523592085236</v>
+        <v>11.92929292929293</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06108343338504127</v>
+        <v>0.1229391992663624</v>
       </c>
       <c r="AC4">
-        <v>-0.06108343338504127</v>
+        <v>-0.1229391992663624</v>
       </c>
       <c r="AD4">
-        <v>66.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>66.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="AG4">
-        <v>-12.89999999999999</v>
+        <v>41.90000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.09567723342939483</v>
+        <v>0.1196690914277564</v>
       </c>
       <c r="AI4">
-        <v>0.1771138970392105</v>
+        <v>0.5695858791581806</v>
       </c>
       <c r="AJ4">
-        <v>-0.02098584675451438</v>
+        <v>0.06357153694431801</v>
       </c>
       <c r="AK4">
-        <v>-0.04364005412719889</v>
+        <v>0.3979107312440646</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-9.85</v>
+        <v>-5.06</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -948,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oyak Yatirim Menkul Degerler A.S. (IBSE:OYYAT)</t>
+          <t>Tera Yatirim Menkul Degerler A.S. (IBSE:TERA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -956,6 +962,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.8140000000000001</v>
+      </c>
+      <c r="E5">
+        <v>0.92</v>
+      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -969,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>26.1</v>
+        <v>3.76</v>
       </c>
       <c r="L5">
-        <v>0.005223342939481268</v>
+        <v>0.05186206896551724</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,61 +1008,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>12</v>
+        <v>21.4</v>
       </c>
       <c r="V5">
-        <v>0.03729024238657551</v>
+        <v>0.3912248628884826</v>
       </c>
       <c r="W5">
-        <v>0.715068493150685</v>
+        <v>0.5295774647887324</v>
       </c>
       <c r="X5">
-        <v>0.06343530601131754</v>
+        <v>0.1293155587401159</v>
       </c>
       <c r="Y5">
-        <v>0.6516331871393675</v>
+        <v>0.4002619060486165</v>
       </c>
       <c r="Z5">
-        <v>105.6405919661734</v>
+        <v>4.092114917875487</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06327508483067738</v>
+        <v>0.1254397544620279</v>
       </c>
       <c r="AC5">
-        <v>-0.06327508483067738</v>
+        <v>-0.1254397544620279</v>
       </c>
       <c r="AD5">
-        <v>51.2</v>
+        <v>11.2</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>51.2</v>
+        <v>11.2</v>
       </c>
       <c r="AG5">
-        <v>39.2</v>
+        <v>-10.2</v>
       </c>
       <c r="AH5">
-        <v>0.1372654155495979</v>
+        <v>0.1699544764795144</v>
       </c>
       <c r="AI5">
-        <v>0.4159220146222583</v>
+        <v>0.6120218579234973</v>
       </c>
       <c r="AJ5">
-        <v>0.1085872576177285</v>
+        <v>-0.2292134831460674</v>
       </c>
       <c r="AK5">
-        <v>0.3528352835283529</v>
+        <v>3.290322580645161</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-4.86</v>
+        <v>-2.09</v>
       </c>
       <c r="AQ5">
         <v>-0</v>
@@ -1072,23 +1084,11 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G6">
-        <v>-0</v>
-      </c>
-      <c r="H6">
-        <v>-0</v>
-      </c>
-      <c r="I6">
-        <v>-0</v>
-      </c>
-      <c r="J6">
-        <v>-0</v>
+      <c r="E6">
+        <v>0.8100000000000001</v>
       </c>
       <c r="K6">
-        <v>0.144</v>
-      </c>
-      <c r="L6">
-        <v>-0.3564356435643564</v>
+        <v>0.299</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1112,61 +1112,61 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="V6">
-        <v>0.0008264462809917356</v>
+        <v>0.0008784773060029283</v>
       </c>
       <c r="W6">
-        <v>0.01762545899632803</v>
+        <v>0.04129834254143646</v>
       </c>
       <c r="X6">
-        <v>0.06832500137743749</v>
+        <v>0.1350587122855602</v>
       </c>
       <c r="Y6">
-        <v>-0.05069954238110946</v>
+        <v>-0.09376036974412369</v>
       </c>
       <c r="Z6">
-        <v>-0.03527768075445337</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06635647886035261</v>
+        <v>0.1284682141320884</v>
       </c>
       <c r="AC6">
-        <v>-0.06635647886035261</v>
+        <v>-0.1284682141320884</v>
       </c>
       <c r="AD6">
-        <v>2.92</v>
+        <v>2.05</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.92</v>
+        <v>2.05</v>
       </c>
       <c r="AG6">
-        <v>2.912</v>
+        <v>2.044</v>
       </c>
       <c r="AH6">
-        <v>0.2317460317460318</v>
+        <v>0.2308558558558559</v>
       </c>
       <c r="AI6">
-        <v>0.2874015748031496</v>
+        <v>0.3528399311531842</v>
       </c>
       <c r="AJ6">
-        <v>0.2312579415501906</v>
+        <v>0.2303358124859139</v>
       </c>
       <c r="AK6">
-        <v>0.2868400315208826</v>
+        <v>0.352170916609235</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1.06</v>
+        <v>-2.66</v>
       </c>
       <c r="AQ6">
         <v>-0</v>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Global Menkul Degerler Anonim Sirketi (IBSE:GLBMD)</t>
+          <t>Is Yatirim Menkul Degerler Anonim Sirketi (IBSE:ISMEN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1188,8 +1188,14 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.343</v>
+      </c>
+      <c r="E7">
+        <v>0.79</v>
+      </c>
       <c r="G7">
-        <v>0</v>
+        <v>1.601650514428428e-05</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1201,88 +1207,91 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>3.36</v>
+        <v>125.2</v>
       </c>
       <c r="L7">
-        <v>0.004530744336569579</v>
+        <v>0.01132918894951634</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>23.8</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.01930094882815668</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.1900958466453674</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>23.8</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.01930094882815668</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.1900958466453674</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>5.61</v>
+        <v>34.3</v>
       </c>
       <c r="V7">
-        <v>0.31875</v>
+        <v>0.02781607331116698</v>
       </c>
       <c r="W7">
-        <v>0.4313222079589217</v>
+        <v>0.4552727272727273</v>
       </c>
       <c r="X7">
-        <v>0.08117058260201879</v>
+        <v>0.1384807701859413</v>
       </c>
       <c r="Y7">
-        <v>0.3501516253569029</v>
+        <v>0.3167919570867859</v>
       </c>
       <c r="Z7">
-        <v>47.69131832797428</v>
+        <v>42.87360335195531</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07256228770297701</v>
+        <v>0.1293005319128492</v>
       </c>
       <c r="AC7">
-        <v>-0.07256228770297701</v>
+        <v>-0.1293005319128492</v>
       </c>
       <c r="AD7">
-        <v>11.9</v>
+        <v>440.2</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>11.9</v>
+        <v>440.2</v>
       </c>
       <c r="AG7">
-        <v>6.29</v>
+        <v>405.9</v>
       </c>
       <c r="AH7">
-        <v>0.4033898305084746</v>
+        <v>0.2630729695810674</v>
       </c>
       <c r="AI7">
-        <v>0.5409090909090909</v>
+        <v>0.6264408709264265</v>
       </c>
       <c r="AJ7">
-        <v>0.2632900795311846</v>
+        <v>0.2476510067114094</v>
       </c>
       <c r="AK7">
-        <v>0.3837705918242831</v>
+        <v>0.6072710951526032</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.6899999999999999</v>
+        <v>-14.8</v>
       </c>
       <c r="AQ7">
         <v>-0</v>
@@ -1296,117 +1305,242 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Global Menkul Degerler Anonim Sirketi (IBSE:GLBMD)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.023</v>
+      </c>
+      <c r="E8">
+        <v>0.212</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.179</v>
+      </c>
+      <c r="L8">
+        <v>0.0003658287349274474</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>-0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>4.45</v>
+      </c>
+      <c r="V8">
+        <v>0.1529209621993127</v>
+      </c>
+      <c r="W8">
+        <v>0.01772277227722772</v>
+      </c>
+      <c r="X8">
+        <v>0.1375739581593114</v>
+      </c>
+      <c r="Y8">
+        <v>-0.1198511858820837</v>
+      </c>
+      <c r="Z8">
+        <v>29.8535692495424</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.1296589675898976</v>
+      </c>
+      <c r="AC8">
+        <v>-0.1296589675898976</v>
+      </c>
+      <c r="AD8">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="AG8">
+        <v>5.499999999999999</v>
+      </c>
+      <c r="AH8">
+        <v>0.2548015364916774</v>
+      </c>
+      <c r="AI8">
+        <v>0.6847900894700619</v>
+      </c>
+      <c r="AJ8">
+        <v>0.1589595375722543</v>
+      </c>
+      <c r="AK8">
+        <v>0.5456349206349206</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>-0.446</v>
+      </c>
+      <c r="AQ8">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Gedik Yatirim Menkul Degerler A.S. (IBSE:GEDIK)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D8">
-        <v>0.716</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>23.6</v>
-      </c>
-      <c r="L8">
-        <v>0.01635481635481635</v>
-      </c>
-      <c r="M8">
-        <v>3.38</v>
-      </c>
-      <c r="N8">
-        <v>0.02213490504256713</v>
-      </c>
-      <c r="O8">
-        <v>0.1432203389830508</v>
-      </c>
-      <c r="P8">
-        <v>3.38</v>
-      </c>
-      <c r="Q8">
-        <v>0.02213490504256713</v>
-      </c>
-      <c r="R8">
-        <v>0.1432203389830508</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>62</v>
-      </c>
-      <c r="V8">
-        <v>0.4060248853962017</v>
-      </c>
-      <c r="W8">
-        <v>0.6610644257703081</v>
-      </c>
-      <c r="X8">
-        <v>0.08879791586525504</v>
-      </c>
-      <c r="Y8">
-        <v>0.572266509905053</v>
-      </c>
-      <c r="Z8">
-        <v>17.61904761904762</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.07508869499610507</v>
-      </c>
-      <c r="AC8">
-        <v>-0.07508869499610507</v>
-      </c>
-      <c r="AD8">
-        <v>137.2</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>137.2</v>
-      </c>
-      <c r="AG8">
-        <v>75.19999999999999</v>
-      </c>
-      <c r="AH8">
-        <v>0.4732666436702311</v>
-      </c>
-      <c r="AI8">
-        <v>0.7266949152542372</v>
-      </c>
-      <c r="AJ8">
-        <v>0.3299692847740237</v>
-      </c>
-      <c r="AK8">
-        <v>0.5930599369085173</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>-6.69</v>
-      </c>
-      <c r="AQ8">
+      <c r="D9">
+        <v>1.702</v>
+      </c>
+      <c r="E9">
+        <v>1.204</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1.77</v>
+      </c>
+      <c r="L9">
+        <v>0.0004957705450675033</v>
+      </c>
+      <c r="M9">
+        <v>6.24</v>
+      </c>
+      <c r="N9">
+        <v>0.03141993957703928</v>
+      </c>
+      <c r="O9">
+        <v>3.525423728813559</v>
+      </c>
+      <c r="P9">
+        <v>4.08</v>
+      </c>
+      <c r="Q9">
+        <v>0.02054380664652568</v>
+      </c>
+      <c r="R9">
+        <v>2.305084745762712</v>
+      </c>
+      <c r="S9">
+        <v>2.16</v>
+      </c>
+      <c r="T9">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="U9">
+        <v>28.8</v>
+      </c>
+      <c r="V9">
+        <v>0.1450151057401813</v>
+      </c>
+      <c r="W9">
+        <v>0.0345703125</v>
+      </c>
+      <c r="X9">
+        <v>0.1601868715599143</v>
+      </c>
+      <c r="Y9">
+        <v>-0.1256165590599143</v>
+      </c>
+      <c r="Z9">
+        <v>28.24525316455697</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.1365403654335027</v>
+      </c>
+      <c r="AC9">
+        <v>-0.1365403654335027</v>
+      </c>
+      <c r="AD9">
+        <v>142.5</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>142.5</v>
+      </c>
+      <c r="AG9">
+        <v>113.7</v>
+      </c>
+      <c r="AH9">
+        <v>0.4177660510114335</v>
+      </c>
+      <c r="AI9">
+        <v>0.7929883138564274</v>
+      </c>
+      <c r="AJ9">
+        <v>0.3640730067243035</v>
+      </c>
+      <c r="AK9">
+        <v>0.7534791252485089</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-7.59</v>
+      </c>
+      <c r="AQ9">
         <v>-0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/turkey/turkey_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.341</v>
+        <v>0.463</v>
       </c>
       <c r="E2">
-        <v>0.92</v>
+        <v>1.175</v>
       </c>
       <c r="G2">
-        <v>1.073653868550798e-05</v>
+        <v>0.000183883161821688</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0001723376646782129</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>0.000166142519869519</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.0001397003842571321</v>
       </c>
       <c r="K2">
-        <v>223.708</v>
+        <v>681.1510000000001</v>
       </c>
       <c r="L2">
-        <v>0.01356977173026903</v>
+        <v>0.03836208255987889</v>
       </c>
       <c r="M2">
-        <v>37.82</v>
+        <v>37.007</v>
       </c>
       <c r="N2">
-        <v>0.01491248477010248</v>
+        <v>0.01303706052279293</v>
       </c>
       <c r="O2">
-        <v>0.1690596670659968</v>
+        <v>0.05433009714439235</v>
       </c>
       <c r="P2">
-        <v>33.28</v>
+        <v>31.577</v>
       </c>
       <c r="Q2">
-        <v>0.01312235571520387</v>
+        <v>0.01112414570562954</v>
       </c>
       <c r="R2">
-        <v>0.1487653548375561</v>
+        <v>0.04635829647170744</v>
       </c>
       <c r="S2">
-        <v>4.54</v>
+        <v>5.43</v>
       </c>
       <c r="T2">
-        <v>0.1200423056583818</v>
+        <v>0.1467289972167428</v>
       </c>
       <c r="U2">
-        <v>130.958</v>
+        <v>467.761</v>
       </c>
       <c r="V2">
-        <v>0.05163694290119197</v>
+        <v>0.1647858099062918</v>
       </c>
       <c r="W2">
-        <v>0.4552727272727273</v>
+        <v>1.29875430858152</v>
       </c>
       <c r="X2">
-        <v>0.1350587122855602</v>
+        <v>0.1037572023581918</v>
       </c>
       <c r="Y2">
-        <v>0.3202140149871671</v>
+        <v>1.194997106223328</v>
       </c>
       <c r="Z2">
-        <v>26.24790830452857</v>
+        <v>15.87565448771137</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1284682141320884</v>
+        <v>0.1016000054619469</v>
       </c>
       <c r="AC2">
-        <v>-0.1284682141320884</v>
+        <v>-0.09983621447162155</v>
       </c>
       <c r="AD2">
-        <v>718.2</v>
+        <v>964.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>718.2</v>
+        <v>964.9</v>
       </c>
       <c r="AG2">
-        <v>587.2420000000001</v>
+        <v>497.139</v>
       </c>
       <c r="AH2">
-        <v>0.2206905876171132</v>
+        <v>0.2536873931904824</v>
       </c>
       <c r="AI2">
-        <v>0.5940741476003772</v>
+        <v>0.4731734348105394</v>
       </c>
       <c r="AJ2">
-        <v>0.1880153884967913</v>
+        <v>0.1490341420596755</v>
       </c>
       <c r="AK2">
-        <v>0.5447604876519275</v>
+        <v>0.3163570691762825</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM2">
-        <v>-34.856</v>
+        <v>-41.943</v>
+      </c>
+      <c r="AN2">
+        <v>320.5647840531562</v>
+      </c>
+      <c r="AO2">
+        <v>1.204081632653061</v>
+      </c>
+      <c r="AP2">
+        <v>165.1624584717608</v>
       </c>
       <c r="AQ2">
-        <v>-0</v>
+        <v>-0.07033354791025917</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Inveo Yatirim Holding Anonim Sirketi (IBSE:INVEO)</t>
+          <t>Seker Yatirim Menkul Degerler A.S. (IBSE:SKYMD)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,113 +721,101 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.339</v>
-      </c>
-      <c r="E3">
-        <v>2.279</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.002868122598181648</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.002868122598181648</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.002765020151841784</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.002219105916734561</v>
       </c>
       <c r="K3">
-        <v>58.6</v>
+        <v>2.19</v>
       </c>
       <c r="L3">
-        <v>16.46067415730337</v>
+        <v>0.002052675977130003</v>
       </c>
       <c r="M3">
-        <v>2.38</v>
+        <v>0.326</v>
       </c>
       <c r="N3">
-        <v>0.006001008572869389</v>
+        <v>0.008787061994609165</v>
       </c>
       <c r="O3">
-        <v>0.04061433447098976</v>
+        <v>0.1488584474885845</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.326</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.008787061994609165</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1488584474885845</v>
       </c>
       <c r="S3">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.002</v>
+        <v>5.85</v>
       </c>
       <c r="V3">
-        <v>5.042864346949067e-06</v>
-      </c>
-      <c r="W3">
-        <v>0.6460859977949284</v>
+        <v>0.1576819407008086</v>
       </c>
       <c r="X3">
-        <v>0.1212995854340401</v>
-      </c>
-      <c r="Y3">
-        <v>0.5247864123608883</v>
-      </c>
-      <c r="Z3">
-        <v>0.03922432789775232</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
+        <v>0.1132791451060232</v>
       </c>
       <c r="AB3">
-        <v>0.1203113334454893</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1203113334454893</v>
+        <v>0.1067358945655563</v>
       </c>
       <c r="AD3">
-        <v>28.4</v>
+        <v>18</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>28.4</v>
+        <v>18</v>
       </c>
       <c r="AG3">
-        <v>28.398</v>
+        <v>12.15</v>
       </c>
       <c r="AH3">
-        <v>0.0668235294117647</v>
+        <v>0.3266787658802178</v>
       </c>
       <c r="AI3">
-        <v>0.2019914651493599</v>
+        <v>0.5787781350482315</v>
       </c>
       <c r="AJ3">
-        <v>0.06681913797241398</v>
+        <v>0.2467005076142132</v>
       </c>
       <c r="AK3">
-        <v>0.2019801135151282</v>
+        <v>0.4811881188118812</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM3">
-        <v>-2.21</v>
+        <v>1.572</v>
+      </c>
+      <c r="AN3">
+        <v>5.980066445182724</v>
+      </c>
+      <c r="AO3">
+        <v>1.204081632653061</v>
+      </c>
+      <c r="AP3">
+        <v>4.036544850498339</v>
       </c>
       <c r="AQ3">
-        <v>-0</v>
+        <v>1.876590330788804</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oyak Yatirim Menkul Degerler A.S. (IBSE:OYYAT)</t>
+          <t>Euro Yatirim Holding A.S. (IBSE:EUHOL)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,11 +834,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.312</v>
-      </c>
       <c r="E4">
-        <v>1.148</v>
+        <v>-0.323</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,91 +850,88 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>33.9</v>
+        <v>0.061</v>
       </c>
       <c r="L4">
-        <v>0.02609498883842661</v>
+        <v>0.4357142857142857</v>
       </c>
       <c r="M4">
-        <v>5.4</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.008749189889825017</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.1592920353982301</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>5.4</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.008749189889825017</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.1592920353982301</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>42</v>
+        <v>0.081</v>
       </c>
       <c r="V4">
-        <v>0.06804925469863901</v>
+        <v>0.01372881355932203</v>
       </c>
       <c r="W4">
-        <v>0.4863701578192252</v>
+        <v>0.01622340425531915</v>
       </c>
       <c r="X4">
-        <v>0.1251724449064209</v>
+        <v>0.09340822694532534</v>
       </c>
       <c r="Y4">
-        <v>0.3611977129128043</v>
+        <v>-0.07718482269000619</v>
       </c>
       <c r="Z4">
-        <v>11.92929292929293</v>
+        <v>0.02412129565816679</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1229391992663624</v>
+        <v>0.09340822694532534</v>
       </c>
       <c r="AC4">
-        <v>-0.1229391992663624</v>
+        <v>-0.09340822694532534</v>
       </c>
       <c r="AD4">
-        <v>83.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>83.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>41.90000000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="AH4">
-        <v>0.1196690914277564</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.5695858791581806</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.06357153694431801</v>
+        <v>-0.01391991751159993</v>
       </c>
       <c r="AK4">
-        <v>0.3979107312440646</v>
+        <v>-0.008473689716497541</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-5.06</v>
+        <v>-0.65</v>
       </c>
       <c r="AQ4">
         <v>-0</v>
@@ -954,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tera Yatirim Menkul Degerler A.S. (IBSE:TERA)</t>
+          <t>Inveo Yatirim Holding Anonim Sirketi (IBSE:INVEO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -962,38 +953,20 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.8140000000000001</v>
-      </c>
       <c r="E5">
-        <v>0.92</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
+        <v>1.997</v>
       </c>
       <c r="K5">
-        <v>3.76</v>
-      </c>
-      <c r="L5">
-        <v>0.05186206896551724</v>
+        <v>178.4</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>3.31</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.009769775678866588</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.01855381165919283</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1005,64 +978,67 @@
         <v>-0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.31</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>21.4</v>
+        <v>1.27</v>
       </c>
       <c r="V5">
-        <v>0.3912248628884826</v>
+        <v>0.003748524203069657</v>
       </c>
       <c r="W5">
-        <v>0.5295774647887324</v>
+        <v>1.590017825311943</v>
       </c>
       <c r="X5">
-        <v>0.1293155587401159</v>
+        <v>0.09697436337143314</v>
       </c>
       <c r="Y5">
-        <v>0.4002619060486165</v>
+        <v>1.49304346194051</v>
       </c>
       <c r="Z5">
-        <v>4.092114917875487</v>
+        <v>0</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.1254397544620279</v>
+        <v>0.09667601246638372</v>
       </c>
       <c r="AC5">
-        <v>-0.1254397544620279</v>
+        <v>-0.09667601246638372</v>
       </c>
       <c r="AD5">
-        <v>11.2</v>
+        <v>29.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>11.2</v>
+        <v>29.5</v>
       </c>
       <c r="AG5">
-        <v>-10.2</v>
+        <v>28.23</v>
       </c>
       <c r="AH5">
-        <v>0.1699544764795144</v>
+        <v>0.08009774640238936</v>
       </c>
       <c r="AI5">
-        <v>0.6120218579234973</v>
+        <v>0.1036178433438707</v>
       </c>
       <c r="AJ5">
-        <v>-0.2292134831460674</v>
+        <v>0.07691469362177478</v>
       </c>
       <c r="AK5">
-        <v>3.290322580645161</v>
+        <v>0.09960131249338461</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-2.09</v>
+        <v>-0.03</v>
       </c>
       <c r="AQ5">
         <v>-0</v>
@@ -1076,7 +1052,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Euro Yatirim Holding A.S. (IBSE:EUHOL)</t>
+          <t>A1 Capital Yatirim Menkul Degerler A.S. (IBSE:A1CAP)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1084,11 +1060,29 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.648</v>
+      </c>
       <c r="E6">
-        <v>0.8100000000000001</v>
+        <v>1.209</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>0.299</v>
+        <v>23.4</v>
+      </c>
+      <c r="L6">
+        <v>0.0419054441260745</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1112,61 +1106,61 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.006</v>
+        <v>33.5</v>
       </c>
       <c r="V6">
-        <v>0.0008784773060029283</v>
+        <v>0.268</v>
       </c>
       <c r="W6">
-        <v>0.04129834254143646</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="X6">
-        <v>0.1350587122855602</v>
+        <v>0.1001578037957676</v>
       </c>
       <c r="Y6">
-        <v>-0.09376036974412369</v>
+        <v>0.5044933589949301</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>8.639950487389758</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1284682141320884</v>
+        <v>0.0991803966679365</v>
       </c>
       <c r="AC6">
-        <v>-0.1284682141320884</v>
+        <v>-0.0991803966679365</v>
       </c>
       <c r="AD6">
-        <v>2.05</v>
+        <v>20.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.05</v>
+        <v>20.6</v>
       </c>
       <c r="AG6">
-        <v>2.044</v>
+        <v>-12.9</v>
       </c>
       <c r="AH6">
-        <v>0.2308558558558559</v>
+        <v>0.1414835164835165</v>
       </c>
       <c r="AI6">
-        <v>0.3528399311531842</v>
+        <v>0.2019607843137255</v>
       </c>
       <c r="AJ6">
-        <v>0.2303358124859139</v>
+        <v>-0.1150758251561106</v>
       </c>
       <c r="AK6">
-        <v>0.352170916609235</v>
+        <v>-0.1883211678832117</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-2.66</v>
+        <v>-1.63</v>
       </c>
       <c r="AQ6">
         <v>-0</v>
@@ -1180,7 +1174,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Is Yatirim Menkul Degerler Anonim Sirketi (IBSE:ISMEN)</t>
+          <t>Global Menkul Degerler Anonim Sirketi (IBSE:GLBMD)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1189,13 +1183,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.343</v>
+        <v>0.189</v>
       </c>
       <c r="E7">
-        <v>0.79</v>
+        <v>0.868</v>
       </c>
       <c r="G7">
-        <v>1.601650514428428e-05</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1207,91 +1201,88 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>125.2</v>
+        <v>4.3</v>
       </c>
       <c r="L7">
-        <v>0.01132918894951634</v>
+        <v>0.00637131426878056</v>
       </c>
       <c r="M7">
-        <v>23.8</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.01930094882815668</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.1900958466453674</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>23.8</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.01930094882815668</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.1900958466453674</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>34.3</v>
+        <v>5.06</v>
       </c>
       <c r="V7">
-        <v>0.02781607331116698</v>
+        <v>0.09844357976653696</v>
       </c>
       <c r="W7">
-        <v>0.4552727272727273</v>
+        <v>0.9388646288209607</v>
       </c>
       <c r="X7">
-        <v>0.1384807701859413</v>
+        <v>0.102013803565114</v>
       </c>
       <c r="Y7">
-        <v>0.3167919570867859</v>
+        <v>0.8368508252558466</v>
       </c>
       <c r="Z7">
-        <v>42.87360335195531</v>
+        <v>66.95436507936509</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.1293005319128492</v>
+        <v>0.1004920322753066</v>
       </c>
       <c r="AC7">
-        <v>-0.1293005319128492</v>
+        <v>-0.1004920322753066</v>
       </c>
       <c r="AD7">
-        <v>440.2</v>
+        <v>10.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>440.2</v>
+        <v>10.8</v>
       </c>
       <c r="AG7">
-        <v>405.9</v>
+        <v>5.740000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.2630729695810674</v>
+        <v>0.1736334405144695</v>
       </c>
       <c r="AI7">
-        <v>0.6264408709264265</v>
+        <v>0.5976757055893747</v>
       </c>
       <c r="AJ7">
-        <v>0.2476510067114094</v>
+        <v>0.1004550227511376</v>
       </c>
       <c r="AK7">
-        <v>0.6072710951526032</v>
+        <v>0.4411990776325904</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-14.8</v>
+        <v>-0.605</v>
       </c>
       <c r="AQ7">
         <v>-0</v>
@@ -1305,7 +1296,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Global Menkul Degerler Anonim Sirketi (IBSE:GLBMD)</t>
+          <t>Is Yatirim Menkul Degerler Anonim Sirketi (IBSE:ISMEN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1314,13 +1305,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.023</v>
+        <v>0.463</v>
       </c>
       <c r="E8">
-        <v>0.212</v>
+        <v>1.175</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1.721502829982701e-05</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1332,88 +1323,91 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0.179</v>
+        <v>345.3</v>
       </c>
       <c r="L8">
-        <v>0.0003658287349274474</v>
+        <v>0.02899682571673301</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>27.5</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.01693662622405617</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.07964089197799015</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>27.5</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.01693662622405617</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.07964089197799015</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>4.45</v>
+        <v>316.9</v>
       </c>
       <c r="V8">
-        <v>0.1529209621993127</v>
+        <v>0.1951715218328509</v>
       </c>
       <c r="W8">
-        <v>0.01772277227722772</v>
+        <v>1.440550688360451</v>
       </c>
       <c r="X8">
-        <v>0.1375739581593114</v>
+        <v>0.1055006011512696</v>
       </c>
       <c r="Y8">
-        <v>-0.1198511858820837</v>
+        <v>1.335050087209181</v>
       </c>
       <c r="Z8">
-        <v>29.8535692495424</v>
+        <v>18.50478617603182</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1296589675898976</v>
+        <v>0.1027079786485873</v>
       </c>
       <c r="AC8">
-        <v>-0.1296589675898976</v>
+        <v>-0.1027079786485873</v>
       </c>
       <c r="AD8">
-        <v>9.949999999999999</v>
+        <v>479.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>9.949999999999999</v>
+        <v>479.4</v>
       </c>
       <c r="AG8">
-        <v>5.499999999999999</v>
+        <v>162.5</v>
       </c>
       <c r="AH8">
-        <v>0.2548015364916774</v>
+        <v>0.2279492178213114</v>
       </c>
       <c r="AI8">
-        <v>0.6847900894700619</v>
+        <v>0.4824393680185167</v>
       </c>
       <c r="AJ8">
-        <v>0.1589595375722543</v>
+        <v>0.09097525473071325</v>
       </c>
       <c r="AK8">
-        <v>0.5456349206349206</v>
+        <v>0.2401004728132388</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-0.446</v>
+        <v>-12.1</v>
       </c>
       <c r="AQ8">
         <v>-0</v>
@@ -1427,120 +1421,245 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Oyak Yatirim Menkul Degerler A.S. (IBSE:OYYAT)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.172</v>
+      </c>
+      <c r="E9">
+        <v>1.143</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>71.5</v>
+      </c>
+      <c r="L9">
+        <v>0.1038489469862019</v>
+      </c>
+      <c r="M9">
+        <v>0.101</v>
+      </c>
+      <c r="N9">
+        <v>0.00024658203125</v>
+      </c>
+      <c r="O9">
+        <v>0.001412587412587413</v>
+      </c>
+      <c r="P9">
+        <v>0.101</v>
+      </c>
+      <c r="Q9">
+        <v>0.00024658203125</v>
+      </c>
+      <c r="R9">
+        <v>0.001412587412587413</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>34.3</v>
+      </c>
+      <c r="V9">
+        <v>0.08374023437499999</v>
+      </c>
+      <c r="W9">
+        <v>1.156957928802589</v>
+      </c>
+      <c r="X9">
+        <v>0.1150562026539367</v>
+      </c>
+      <c r="Y9">
+        <v>1.041901726148653</v>
+      </c>
+      <c r="Z9">
+        <v>6.639344262295083</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.1075156420007725</v>
+      </c>
+      <c r="AC9">
+        <v>-0.1075156420007725</v>
+      </c>
+      <c r="AD9">
+        <v>216.5</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>216.5</v>
+      </c>
+      <c r="AG9">
+        <v>182.2</v>
+      </c>
+      <c r="AH9">
+        <v>0.3457914071234627</v>
+      </c>
+      <c r="AI9">
+        <v>0.6532890766445384</v>
+      </c>
+      <c r="AJ9">
+        <v>0.307874281851977</v>
+      </c>
+      <c r="AK9">
+        <v>0.6132615281050151</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-14.6</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Gedik Yatirim Menkul Degerler A.S. (IBSE:GEDIK)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D9">
-        <v>1.702</v>
-      </c>
-      <c r="E9">
-        <v>1.204</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>1.77</v>
-      </c>
-      <c r="L9">
-        <v>0.0004957705450675033</v>
-      </c>
-      <c r="M9">
-        <v>6.24</v>
-      </c>
-      <c r="N9">
-        <v>0.03141993957703928</v>
-      </c>
-      <c r="O9">
-        <v>3.525423728813559</v>
-      </c>
-      <c r="P9">
-        <v>4.08</v>
-      </c>
-      <c r="Q9">
-        <v>0.02054380664652568</v>
-      </c>
-      <c r="R9">
-        <v>2.305084745762712</v>
-      </c>
-      <c r="S9">
-        <v>2.16</v>
-      </c>
-      <c r="T9">
-        <v>0.3461538461538461</v>
-      </c>
-      <c r="U9">
-        <v>28.8</v>
-      </c>
-      <c r="V9">
-        <v>0.1450151057401813</v>
-      </c>
-      <c r="W9">
-        <v>0.0345703125</v>
-      </c>
-      <c r="X9">
-        <v>0.1601868715599143</v>
-      </c>
-      <c r="Y9">
-        <v>-0.1256165590599143</v>
-      </c>
-      <c r="Z9">
-        <v>28.24525316455697</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.1365403654335027</v>
-      </c>
-      <c r="AC9">
-        <v>-0.1365403654335027</v>
-      </c>
-      <c r="AD9">
-        <v>142.5</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>142.5</v>
-      </c>
-      <c r="AG9">
-        <v>113.7</v>
-      </c>
-      <c r="AH9">
-        <v>0.4177660510114335</v>
-      </c>
-      <c r="AI9">
-        <v>0.7929883138564274</v>
-      </c>
-      <c r="AJ9">
-        <v>0.3640730067243035</v>
-      </c>
-      <c r="AK9">
-        <v>0.7534791252485089</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-7.59</v>
-      </c>
-      <c r="AQ9">
+      <c r="D10">
+        <v>1.149</v>
+      </c>
+      <c r="E10">
+        <v>1.312</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>56</v>
+      </c>
+      <c r="L10">
+        <v>0.01958863858961802</v>
+      </c>
+      <c r="M10">
+        <v>5.77</v>
+      </c>
+      <c r="N10">
+        <v>0.02335087009307972</v>
+      </c>
+      <c r="O10">
+        <v>0.1030357142857143</v>
+      </c>
+      <c r="P10">
+        <v>3.65</v>
+      </c>
+      <c r="Q10">
+        <v>0.01477134763253743</v>
+      </c>
+      <c r="R10">
+        <v>0.06517857142857143</v>
+      </c>
+      <c r="S10">
+        <v>2.12</v>
+      </c>
+      <c r="T10">
+        <v>0.3674176776429809</v>
+      </c>
+      <c r="U10">
+        <v>70.8</v>
+      </c>
+      <c r="V10">
+        <v>0.2865236746256576</v>
+      </c>
+      <c r="W10">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="X10">
+        <v>0.1249167981987845</v>
+      </c>
+      <c r="Y10">
+        <v>1.413544740262754</v>
+      </c>
+      <c r="Z10">
+        <v>19.04596935376416</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.1111474751618529</v>
+      </c>
+      <c r="AC10">
+        <v>-0.1111474751618529</v>
+      </c>
+      <c r="AD10">
+        <v>190.1</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>190.1</v>
+      </c>
+      <c r="AG10">
+        <v>119.3</v>
+      </c>
+      <c r="AH10">
+        <v>0.4348124428179323</v>
+      </c>
+      <c r="AI10">
+        <v>0.7077438570364853</v>
+      </c>
+      <c r="AJ10">
+        <v>0.3256004366812227</v>
+      </c>
+      <c r="AK10">
+        <v>0.6031344792719918</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>-13.9</v>
+      </c>
+      <c r="AQ10">
         <v>-0</v>
       </c>
     </row>
